--- a/research/traditional_assets/database/data/rwanda/rwanda_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/rwanda/rwanda_bank_money_center.xlsx
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.138</v>
+        <v>0.186</v>
       </c>
       <c r="E2">
-        <v>0.178</v>
+        <v>0.201</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -606,82 +606,85 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>47.7</v>
+        <v>51.5</v>
       </c>
       <c r="L2">
-        <v>0.3797770700636943</v>
+        <v>0.3705035971223021</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>25.326</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>0.1096838458207016</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>0.4917669902912621</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>25.326</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>0.1096838458207016</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.4917669902912621</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
       <c r="U2">
-        <v>90.40000000000001</v>
+        <v>102.6</v>
       </c>
       <c r="V2">
-        <v>0.3899913718723037</v>
+        <v>0.444348202685145</v>
       </c>
       <c r="W2">
-        <v>0.1924162968939089</v>
+        <v>0.1955943790353209</v>
       </c>
       <c r="X2">
-        <v>0.08092852269125833</v>
+        <v>0.1185938914682266</v>
       </c>
       <c r="Y2">
-        <v>0.1114877742026505</v>
+        <v>0.07700048756709428</v>
       </c>
       <c r="Z2">
-        <v>0.3343092893265903</v>
+        <v>0.5001799208348328</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.07552716422015011</v>
+        <v>0.1127178275992221</v>
       </c>
       <c r="AC2">
-        <v>-0.07552716422015011</v>
+        <v>-0.1127178275992221</v>
       </c>
       <c r="AD2">
-        <v>59.5</v>
+        <v>55.5</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>59.5</v>
+        <v>55.5</v>
       </c>
       <c r="AG2">
-        <v>-30.90000000000001</v>
+        <v>-47.09999999999999</v>
       </c>
       <c r="AH2">
-        <v>0.2042567799519396</v>
+        <v>0.1937849162011173</v>
       </c>
       <c r="AI2">
-        <v>0.1757235676314235</v>
+        <v>0.1639586410635155</v>
       </c>
       <c r="AJ2">
-        <v>-0.1538078646092584</v>
+        <v>-0.2562568008705114</v>
       </c>
       <c r="AK2">
-        <v>-0.1244963738920226</v>
+        <v>-0.1996608732513777</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -707,10 +710,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.138</v>
+        <v>0.186</v>
       </c>
       <c r="E3">
-        <v>0.178</v>
+        <v>0.201</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -725,82 +728,85 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>47.7</v>
+        <v>51.5</v>
       </c>
       <c r="L3">
-        <v>0.3797770700636943</v>
+        <v>0.3705035971223021</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>25.326</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.1096838458207016</v>
       </c>
       <c r="O3">
-        <v>-0</v>
+        <v>0.4917669902912621</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>25.326</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.1096838458207016</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>0.4917669902912621</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
       <c r="U3">
-        <v>90.40000000000001</v>
+        <v>102.6</v>
       </c>
       <c r="V3">
-        <v>0.3899913718723037</v>
+        <v>0.444348202685145</v>
       </c>
       <c r="W3">
-        <v>0.1924162968939089</v>
+        <v>0.1955943790353209</v>
       </c>
       <c r="X3">
-        <v>0.08092852269125833</v>
+        <v>0.1185938914682266</v>
       </c>
       <c r="Y3">
-        <v>0.1114877742026505</v>
+        <v>0.07700048756709428</v>
       </c>
       <c r="Z3">
-        <v>0.3343092893265903</v>
+        <v>0.5001799208348328</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.07552716422015011</v>
+        <v>0.1127178275992221</v>
       </c>
       <c r="AC3">
-        <v>-0.07552716422015011</v>
+        <v>-0.1127178275992221</v>
       </c>
       <c r="AD3">
-        <v>59.5</v>
+        <v>55.5</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>59.5</v>
+        <v>55.5</v>
       </c>
       <c r="AG3">
-        <v>-30.90000000000001</v>
+        <v>-47.09999999999999</v>
       </c>
       <c r="AH3">
-        <v>0.2042567799519396</v>
+        <v>0.1937849162011173</v>
       </c>
       <c r="AI3">
-        <v>0.1757235676314235</v>
+        <v>0.1639586410635155</v>
       </c>
       <c r="AJ3">
-        <v>-0.1538078646092584</v>
+        <v>-0.2562568008705114</v>
       </c>
       <c r="AK3">
-        <v>-0.1244963738920226</v>
+        <v>-0.1996608732513777</v>
       </c>
       <c r="AL3">
         <v>0</v>

--- a/research/traditional_assets/database/data/rwanda/rwanda_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/rwanda/rwanda_bank_money_center.xlsx
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.186</v>
+        <v>0.192</v>
       </c>
       <c r="E2">
-        <v>0.201</v>
+        <v>0.227</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -606,85 +606,82 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>51.5</v>
+        <v>58.2</v>
       </c>
       <c r="L2">
-        <v>0.3705035971223021</v>
+        <v>0.3537993920972645</v>
       </c>
       <c r="M2">
-        <v>25.326</v>
+        <v>0</v>
       </c>
       <c r="N2">
-        <v>0.1096838458207016</v>
+        <v>0</v>
       </c>
       <c r="O2">
-        <v>0.4917669902912621</v>
+        <v>0</v>
       </c>
       <c r="P2">
-        <v>25.326</v>
+        <v>0</v>
       </c>
       <c r="Q2">
-        <v>0.1096838458207016</v>
+        <v>0</v>
       </c>
       <c r="R2">
-        <v>0.4917669902912621</v>
+        <v>0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
-      <c r="T2">
-        <v>0</v>
-      </c>
       <c r="U2">
-        <v>102.6</v>
+        <v>295.4</v>
       </c>
       <c r="V2">
-        <v>0.444348202685145</v>
+        <v>1.407336827060505</v>
       </c>
       <c r="W2">
-        <v>0.1955943790353209</v>
+        <v>0.1958277254374159</v>
       </c>
       <c r="X2">
-        <v>0.1185938914682266</v>
+        <v>0.1033139323432182</v>
       </c>
       <c r="Y2">
-        <v>0.07700048756709428</v>
+        <v>0.09251379309419765</v>
       </c>
       <c r="Z2">
-        <v>0.5001799208348328</v>
+        <v>1.742584745762712</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.1127178275992221</v>
+        <v>0.09565340950460326</v>
       </c>
       <c r="AC2">
-        <v>-0.1127178275992221</v>
+        <v>-0.09565340950460326</v>
       </c>
       <c r="AD2">
-        <v>55.5</v>
+        <v>88.8</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>55.5</v>
+        <v>88.8</v>
       </c>
       <c r="AG2">
-        <v>-47.09999999999999</v>
+        <v>-206.6</v>
       </c>
       <c r="AH2">
-        <v>0.1937849162011173</v>
+        <v>0.2972882490793438</v>
       </c>
       <c r="AI2">
-        <v>0.1639586410635155</v>
+        <v>0.2368631635102694</v>
       </c>
       <c r="AJ2">
-        <v>-0.2562568008705114</v>
+        <v>-62.60606060605984</v>
       </c>
       <c r="AK2">
-        <v>-0.1996608732513777</v>
+        <v>-2.598742138364778</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -710,10 +707,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.186</v>
+        <v>0.192</v>
       </c>
       <c r="E3">
-        <v>0.201</v>
+        <v>0.227</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -728,85 +725,82 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>51.5</v>
+        <v>58.2</v>
       </c>
       <c r="L3">
-        <v>0.3705035971223021</v>
+        <v>0.3537993920972645</v>
       </c>
       <c r="M3">
-        <v>25.326</v>
+        <v>-0</v>
       </c>
       <c r="N3">
-        <v>0.1096838458207016</v>
+        <v>-0</v>
       </c>
       <c r="O3">
-        <v>0.4917669902912621</v>
+        <v>-0</v>
       </c>
       <c r="P3">
-        <v>25.326</v>
+        <v>-0</v>
       </c>
       <c r="Q3">
-        <v>0.1096838458207016</v>
+        <v>-0</v>
       </c>
       <c r="R3">
-        <v>0.4917669902912621</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
       <c r="U3">
-        <v>102.6</v>
+        <v>295.4</v>
       </c>
       <c r="V3">
-        <v>0.444348202685145</v>
+        <v>1.407336827060505</v>
       </c>
       <c r="W3">
-        <v>0.1955943790353209</v>
+        <v>0.1958277254374159</v>
       </c>
       <c r="X3">
-        <v>0.1185938914682266</v>
+        <v>0.1033139323432182</v>
       </c>
       <c r="Y3">
-        <v>0.07700048756709428</v>
+        <v>0.09251379309419765</v>
       </c>
       <c r="Z3">
-        <v>0.5001799208348328</v>
+        <v>1.742584745762712</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.1127178275992221</v>
+        <v>0.09565340950460326</v>
       </c>
       <c r="AC3">
-        <v>-0.1127178275992221</v>
+        <v>-0.09565340950460326</v>
       </c>
       <c r="AD3">
-        <v>55.5</v>
+        <v>88.8</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>55.5</v>
+        <v>88.8</v>
       </c>
       <c r="AG3">
-        <v>-47.09999999999999</v>
+        <v>-206.6</v>
       </c>
       <c r="AH3">
-        <v>0.1937849162011173</v>
+        <v>0.2972882490793438</v>
       </c>
       <c r="AI3">
-        <v>0.1639586410635155</v>
+        <v>0.2368631635102694</v>
       </c>
       <c r="AJ3">
-        <v>-0.2562568008705114</v>
+        <v>-62.60606060605984</v>
       </c>
       <c r="AK3">
-        <v>-0.1996608732513777</v>
+        <v>-2.598742138364778</v>
       </c>
       <c r="AL3">
         <v>0</v>
